--- a/models/xls/BeModelClinicalObservation.xlsx
+++ b/models/xls/BeModelClinicalObservation.xlsx
@@ -500,7 +500,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -936,23 +935,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1243,6 +1230,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Performer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1428,6 +1425,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UsedDevice</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1463,6 +1470,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1498,6 +1515,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1603,6 +1630,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1778,6 +1815,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>BodyLocation</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1846,6 +1893,16 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>*</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
